--- a/assets/infobasica/planilhas/aula13_nivel3.xlsx
+++ b/assets/infobasica/planilhas/aula13_nivel3.xlsx
@@ -560,7 +560,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tabuada: número em B1, =SEQUÊNCIA(10) em A3 e =$B$1A3 em B3, arrastada para baixo (o $ fixa a célula).</t>
+          <t>Tabuada: número em B1, =SEQUÊNCIA(10) em A3 e =$B$1*A3 em B3, arrastada para baixo (o $ fixa a célula).</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Para abrir no Google Planilhas: Google Drive → Novo → Upload de arquivo; depois clique no arquivo → Abrir com → Planilhas Google.</t>
+          <t>Esta é a sua cópia: altere à vontade.</t>
         </is>
       </c>
     </row>
